--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DFS_HRM-2031-0192/panel_11/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DFS_HRM-2031-0192/panel_11/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.90301</v>
+        <v>17.01062</v>
       </c>
       <c r="D2" t="n">
-        <v>16.69773</v>
+        <v>16.74439</v>
       </c>
       <c r="E2" t="n">
-        <v>16.75905</v>
+        <v>16.88708</v>
       </c>
       <c r="F2" t="n">
-        <v>42.68908</v>
+        <v>42.28243</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05259</v>
+        <v>0.05212</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81279</v>
+        <v>1.83949</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.98473</v>
+        <v>17.02612</v>
       </c>
       <c r="D3" t="n">
-        <v>16.71349</v>
+        <v>16.84617</v>
       </c>
       <c r="E3" t="n">
-        <v>17.09921</v>
+        <v>16.8719</v>
       </c>
       <c r="F3" t="n">
-        <v>42.48648</v>
+        <v>43.43219</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05249</v>
+        <v>0.05136</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83074</v>
+        <v>1.86385</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.32527</v>
+        <v>17.17548</v>
       </c>
       <c r="D4" t="n">
-        <v>16.643</v>
+        <v>16.79875</v>
       </c>
       <c r="E4" t="n">
-        <v>16.85914</v>
+        <v>16.90539</v>
       </c>
       <c r="F4" t="n">
-        <v>43.18021</v>
+        <v>43.12444</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05188</v>
+        <v>0.05163</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85985</v>
+        <v>1.83418</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.87445</v>
+        <v>17.01013</v>
       </c>
       <c r="D5" t="n">
-        <v>16.7971</v>
+        <v>16.70868</v>
       </c>
       <c r="E5" t="n">
-        <v>16.78336</v>
+        <v>16.87934</v>
       </c>
       <c r="F5" t="n">
-        <v>42.67384</v>
+        <v>43.07976</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05147</v>
+        <v>0.05139</v>
       </c>
       <c r="H5" t="n">
-        <v>1.79736</v>
+        <v>1.85705</v>
       </c>
     </row>
     <row r="6">
@@ -559,10 +559,23 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>scratched - not measurable</t>
-        </is>
+      <c r="C6" t="n">
+        <v>17.11481</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16.77508</v>
+      </c>
+      <c r="E6" t="n">
+        <v>16.96972</v>
+      </c>
+      <c r="F6" t="n">
+        <v>43.13173</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.05111</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.85759</v>
       </c>
     </row>
     <row r="7">
@@ -572,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.84093</v>
+        <v>17.12027</v>
       </c>
       <c r="D7" t="n">
-        <v>16.95005</v>
+        <v>16.84999</v>
       </c>
       <c r="E7" t="n">
-        <v>17.07271</v>
+        <v>16.96957</v>
       </c>
       <c r="F7" t="n">
-        <v>42.36114</v>
+        <v>43.29466</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05129</v>
+        <v>0.05144</v>
       </c>
       <c r="H7" t="n">
-        <v>1.85928</v>
+        <v>1.80285</v>
       </c>
     </row>
     <row r="8">
@@ -597,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.01862</v>
+        <v>17.11617</v>
       </c>
       <c r="D8" t="n">
-        <v>16.69412</v>
+        <v>16.83575</v>
       </c>
       <c r="E8" t="n">
-        <v>16.86174</v>
+        <v>16.95833</v>
       </c>
       <c r="F8" t="n">
-        <v>43.17288</v>
+        <v>43.04084</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0506</v>
+        <v>0.05137</v>
       </c>
       <c r="H8" t="n">
-        <v>1.81008</v>
+        <v>1.84948</v>
       </c>
     </row>
     <row r="9">
@@ -622,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.07515</v>
+        <v>17.12849</v>
       </c>
       <c r="D9" t="n">
-        <v>16.56799</v>
+        <v>16.52806</v>
       </c>
       <c r="E9" t="n">
-        <v>16.72664</v>
+        <v>16.96671</v>
       </c>
       <c r="F9" t="n">
-        <v>43.49333</v>
+        <v>43.09326</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05077</v>
+        <v>0.05086</v>
       </c>
       <c r="H9" t="n">
-        <v>1.81615</v>
+        <v>1.79861</v>
       </c>
     </row>
     <row r="10">
@@ -647,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.77216</v>
+        <v>17.1515</v>
       </c>
       <c r="D10" t="n">
-        <v>16.55989</v>
+        <v>16.61895</v>
       </c>
       <c r="E10" t="n">
-        <v>16.95798</v>
+        <v>16.99543</v>
       </c>
       <c r="F10" t="n">
-        <v>43.54419</v>
+        <v>42.77337</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05255</v>
+        <v>0.05172</v>
       </c>
       <c r="H10" t="n">
-        <v>1.82621</v>
+        <v>1.80882</v>
       </c>
     </row>
     <row r="11">
@@ -683,12 +696,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -700,23 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.07896</v>
+        <v>17.27048</v>
       </c>
       <c r="D12" t="n">
-        <v>15.97922</v>
+        <v>16.75561</v>
       </c>
       <c r="E12" t="n">
-        <v>16.74782</v>
+        <v>16.99212</v>
       </c>
       <c r="F12" t="n">
-        <v>22.3504</v>
+        <v>42.66481</v>
       </c>
       <c r="G12" t="n">
-        <v>34.11776</v>
+        <v>0.05213</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.81701</v>
       </c>
     </row>
     <row r="13">
@@ -726,19 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.29785</v>
+        <v>17.05945</v>
       </c>
       <c r="D13" t="n">
-        <v>16.29481</v>
+        <v>16.81278</v>
       </c>
       <c r="E13" t="n">
-        <v>16.56451</v>
+        <v>17.0255</v>
       </c>
       <c r="F13" t="n">
-        <v>21.62265</v>
+        <v>42.79737</v>
       </c>
       <c r="G13" t="n">
-        <v>34.13889</v>
+        <v>0.05066</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.84466</v>
       </c>
     </row>
     <row r="14">
@@ -747,25 +771,23 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>re-measured</t>
-        </is>
-      </c>
       <c r="C14" t="n">
-        <v>16.91799</v>
+        <v>17.00016</v>
       </c>
       <c r="D14" t="n">
-        <v>16.3874</v>
+        <v>16.83813</v>
       </c>
       <c r="E14" t="n">
-        <v>16.59296</v>
+        <v>16.97118</v>
       </c>
       <c r="F14" t="n">
-        <v>21.58099</v>
+        <v>43.75498</v>
       </c>
       <c r="G14" t="n">
-        <v>34.47347</v>
+        <v>0.05099</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.8428</v>
       </c>
     </row>
     <row r="15">
@@ -775,19 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.10722</v>
+        <v>17.26302</v>
       </c>
       <c r="D15" t="n">
-        <v>15.99346</v>
+        <v>16.9289</v>
       </c>
       <c r="E15" t="n">
-        <v>16.54612</v>
+        <v>17.13314</v>
       </c>
       <c r="F15" t="n">
-        <v>22.64293</v>
+        <v>43.57411</v>
       </c>
       <c r="G15" t="n">
-        <v>33.42908</v>
+        <v>0.05061</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.8479</v>
       </c>
     </row>
     <row r="16">
@@ -797,19 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.36173</v>
+        <v>16.85621</v>
       </c>
       <c r="D16" t="n">
-        <v>16.61002</v>
+        <v>16.73689</v>
       </c>
       <c r="E16" t="n">
-        <v>16.46707</v>
+        <v>16.84215</v>
       </c>
       <c r="F16" t="n">
-        <v>22.18381</v>
+        <v>42.70194</v>
       </c>
       <c r="G16" t="n">
-        <v>33.84441</v>
+        <v>0.05188</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.83725</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.95572</v>
+        <v>16.93025</v>
       </c>
       <c r="D17" t="n">
-        <v>15.96738</v>
+        <v>16.54004</v>
       </c>
       <c r="E17" t="n">
-        <v>16.71986</v>
+        <v>16.64617</v>
       </c>
       <c r="F17" t="n">
-        <v>21.78117</v>
+        <v>44.31717</v>
       </c>
       <c r="G17" t="n">
-        <v>33.53329</v>
+        <v>0.05186</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.83981</v>
       </c>
     </row>
     <row r="18">
@@ -841,19 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.15979</v>
+        <v>17.04081</v>
       </c>
       <c r="D18" t="n">
-        <v>15.89634</v>
+        <v>16.39809</v>
       </c>
       <c r="E18" t="n">
-        <v>16.32283</v>
+        <v>16.99762</v>
       </c>
       <c r="F18" t="n">
-        <v>21.69774</v>
+        <v>43.38792</v>
       </c>
       <c r="G18" t="n">
-        <v>34.30578</v>
+        <v>0.0515</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.82872</v>
       </c>
     </row>
     <row r="19">
@@ -863,19 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.98431</v>
+        <v>17.03443</v>
       </c>
       <c r="D19" t="n">
-        <v>16.41353</v>
+        <v>16.95278</v>
       </c>
       <c r="E19" t="n">
-        <v>16.58614</v>
+        <v>17.01069</v>
       </c>
       <c r="F19" t="n">
-        <v>22.26675</v>
+        <v>43.05077</v>
       </c>
       <c r="G19" t="n">
-        <v>34.88343</v>
+        <v>0.04982</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.83267</v>
       </c>
     </row>
     <row r="20">
@@ -885,60 +922,43 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.20326</v>
+        <v>16.99474</v>
       </c>
       <c r="D20" t="n">
-        <v>16.35804</v>
+        <v>16.59304</v>
       </c>
       <c r="E20" t="n">
-        <v>16.60342</v>
+        <v>16.83321</v>
       </c>
       <c r="F20" t="n">
-        <v>22.00694</v>
+        <v>42.71739</v>
       </c>
       <c r="G20" t="n">
-        <v>35.02225</v>
+        <v>0.05108</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.83957</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rz mean</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rz min</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Radius</t>
         </is>
       </c>
     </row>
@@ -950,32 +970,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>SR Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.76275</v>
+        <v>16.25267</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08212999999999999</v>
+        <v>15.58307</v>
       </c>
       <c r="E22" t="n">
-        <v>0.61514</v>
+        <v>15.91599</v>
       </c>
       <c r="F22" t="n">
-        <v>0.97763</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.1071</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.00754</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.09372999999999999</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.12651</v>
+        <v>260.62692</v>
       </c>
     </row>
     <row r="23">
@@ -985,28 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.75681</v>
+        <v>16.1093</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08092000000000001</v>
+        <v>15.87358</v>
       </c>
       <c r="E23" t="n">
-        <v>0.62503</v>
+        <v>15.94967</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9677</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.11084</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.007860000000000001</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.0936</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.12664</v>
+        <v>257.50087</v>
       </c>
     </row>
     <row r="24">
@@ -1016,28 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.75841</v>
+        <v>16.17698</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08087</v>
+        <v>15.72963</v>
       </c>
       <c r="E24" t="n">
-        <v>0.62279</v>
+        <v>15.79554</v>
       </c>
       <c r="F24" t="n">
-        <v>0.96959</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.10986</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.00781</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09536</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.12903</v>
+        <v>256.1322</v>
       </c>
     </row>
     <row r="25">
@@ -1047,28 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.7667</v>
+        <v>16.05701</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08307</v>
+        <v>15.80946</v>
       </c>
       <c r="E25" t="n">
-        <v>0.60867</v>
+        <v>15.83264</v>
       </c>
       <c r="F25" t="n">
-        <v>0.98322</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.11156</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.00765</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.12976</v>
+        <v>258.9317</v>
       </c>
     </row>
     <row r="26">
@@ -1078,28 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.74895</v>
+        <v>15.86933</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08282</v>
+        <v>15.60607</v>
       </c>
       <c r="E26" t="n">
-        <v>0.61397</v>
+        <v>15.81947</v>
       </c>
       <c r="F26" t="n">
-        <v>0.97598</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.11003</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.00744</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09415</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.129</v>
+        <v>259.49758</v>
       </c>
     </row>
     <row r="27">
@@ -1109,28 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.7593800000000001</v>
+        <v>16.13701</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08187999999999999</v>
+        <v>15.85404</v>
       </c>
       <c r="E27" t="n">
-        <v>0.61557</v>
+        <v>15.87075</v>
       </c>
       <c r="F27" t="n">
-        <v>0.97312</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.11003</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.00768</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09582</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.12781</v>
+        <v>258.53339</v>
       </c>
     </row>
     <row r="28">
@@ -1140,28 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.74885</v>
+        <v>15.93065</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08042000000000001</v>
+        <v>15.71103</v>
       </c>
       <c r="E28" t="n">
-        <v>0.60955</v>
+        <v>15.73876</v>
       </c>
       <c r="F28" t="n">
-        <v>0.97359</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.11282</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.00772</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09261</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.12861</v>
+        <v>260.60944</v>
       </c>
     </row>
     <row r="29">
@@ -1171,28 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.75753</v>
+        <v>15.95855</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08101999999999999</v>
+        <v>15.72343</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6266699999999999</v>
+        <v>15.76254</v>
       </c>
       <c r="F29" t="n">
-        <v>0.97671</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.11063</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.00784</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09367</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.12703</v>
+        <v>258.02595</v>
       </c>
     </row>
     <row r="30">
@@ -1202,28 +1126,1070 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.76388</v>
+        <v>16.29246</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08235000000000001</v>
+        <v>15.60678</v>
       </c>
       <c r="E30" t="n">
-        <v>0.61883</v>
+        <v>16.13839</v>
       </c>
       <c r="F30" t="n">
-        <v>0.97787</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.11146</v>
-      </c>
-      <c r="H30" t="n">
+        <v>254.0184</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16.65736</v>
+      </c>
+      <c r="D32" t="n">
+        <v>16.12474</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.4572</v>
+      </c>
+      <c r="F32" t="n">
+        <v>22.24725</v>
+      </c>
+      <c r="G32" t="n">
+        <v>34.72686</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16.51404</v>
+      </c>
+      <c r="D33" t="n">
+        <v>16.42367</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.43683</v>
+      </c>
+      <c r="F33" t="n">
+        <v>21.93245</v>
+      </c>
+      <c r="G33" t="n">
+        <v>34.82212</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>17.28674</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.19412</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.42529</v>
+      </c>
+      <c r="F34" t="n">
+        <v>22.15086</v>
+      </c>
+      <c r="G34" t="n">
+        <v>34.78586</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>16.88455</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.36479</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.78412</v>
+      </c>
+      <c r="F35" t="n">
+        <v>21.70619</v>
+      </c>
+      <c r="G35" t="n">
+        <v>33.99591</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.90846</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16.38093</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.72453</v>
+      </c>
+      <c r="F36" t="n">
+        <v>22.24496</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34.71844</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>17.05107</v>
+      </c>
+      <c r="D37" t="n">
+        <v>15.81908</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.55364</v>
+      </c>
+      <c r="F37" t="n">
+        <v>21.95235</v>
+      </c>
+      <c r="G37" t="n">
+        <v>35.1789</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>17.1931</v>
+      </c>
+      <c r="D38" t="n">
+        <v>16.03632</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.77935</v>
+      </c>
+      <c r="F38" t="n">
+        <v>21.85176</v>
+      </c>
+      <c r="G38" t="n">
+        <v>34.65298</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.96507</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.12918</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.57423</v>
+      </c>
+      <c r="F39" t="n">
+        <v>22.16097</v>
+      </c>
+      <c r="G39" t="n">
+        <v>33.9353</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>17.07968</v>
+      </c>
+      <c r="D40" t="n">
+        <v>16.01925</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.6034</v>
+      </c>
+      <c r="F40" t="n">
+        <v>22.10099</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34.84207</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>17.36584</v>
+      </c>
+      <c r="D42" t="n">
+        <v>16.29959</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.58284</v>
+      </c>
+      <c r="F42" t="n">
+        <v>22.24147</v>
+      </c>
+      <c r="G42" t="n">
+        <v>34.52735</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>17.00767</v>
+      </c>
+      <c r="D43" t="n">
+        <v>16.19733</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.46686</v>
+      </c>
+      <c r="F43" t="n">
+        <v>22.57384</v>
+      </c>
+      <c r="G43" t="n">
+        <v>34.80504</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.82247</v>
+      </c>
+      <c r="D44" t="n">
+        <v>16.20174</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.41663</v>
+      </c>
+      <c r="F44" t="n">
+        <v>22.29209</v>
+      </c>
+      <c r="G44" t="n">
+        <v>34.16583</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16.79247</v>
+      </c>
+      <c r="D45" t="n">
+        <v>16.12363</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.42981</v>
+      </c>
+      <c r="F45" t="n">
+        <v>22.23622</v>
+      </c>
+      <c r="G45" t="n">
+        <v>34.3778</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>17.0509</v>
+      </c>
+      <c r="D46" t="n">
+        <v>16.16586</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.7792</v>
+      </c>
+      <c r="F46" t="n">
+        <v>22.13936</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34.30006</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>16.70844</v>
+      </c>
+      <c r="D47" t="n">
+        <v>16.19818</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.52157</v>
+      </c>
+      <c r="F47" t="n">
+        <v>22.2217</v>
+      </c>
+      <c r="G47" t="n">
+        <v>34.76835</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>17.48141</v>
+      </c>
+      <c r="D48" t="n">
+        <v>16.09719</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.44661</v>
+      </c>
+      <c r="F48" t="n">
+        <v>22.26238</v>
+      </c>
+      <c r="G48" t="n">
+        <v>34.11933</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>17.21775</v>
+      </c>
+      <c r="D49" t="n">
+        <v>16.19814</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.20336</v>
+      </c>
+      <c r="F49" t="n">
+        <v>21.99851</v>
+      </c>
+      <c r="G49" t="n">
+        <v>34.07722</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.94088</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16.20844</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.84094</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.80478</v>
+      </c>
+      <c r="G50" t="n">
+        <v>35.14311</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.60919</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.14292</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.61781</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.133</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.61492</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.11967</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.62109</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.11367</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.61802</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.122</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.61564</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.14352</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.61981</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.1209</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.59971</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.11171</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.6218399999999999</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.14646</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.61385</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.1541</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.61621</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.14302</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.61425</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.14923</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.6069099999999999</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.1233</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.6192</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.12107</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.61188</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.11675</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.62304</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.12317</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.6202800000000001</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.12668</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.60847</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.13494</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.74417</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.08369</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.6078</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.98051</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.1087</v>
+      </c>
+      <c r="H72" t="n">
         <v>0.00774</v>
       </c>
-      <c r="I30" t="n">
-        <v>0.09103</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.12831</v>
+      <c r="I72" t="n">
+        <v>0.09249</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.12804</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.75196</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.08233</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.61252</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.96158</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.10933</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.09248000000000001</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.74249</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.08218</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.60824</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.98721</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.10897</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.00778</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.09344</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.13082</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.75512</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.0833</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.61424</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.97985</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.1099</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.00768</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.09335</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.12599</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.75043</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.08105999999999999</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.62736</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.9686399999999999</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.11066</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.00774</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.09354</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.12638</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.7442800000000001</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.08182</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.6257200000000001</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.10786</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.00776</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.09163</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.12861</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.76523</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.08135000000000001</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.62295</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.97829</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.10947</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.00767</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.09368</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.12727</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.75162</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.08130999999999999</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.63103</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.95675</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.1105</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.00764</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.09533999999999999</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.12645</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.77683</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.08137</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.62621</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.96408</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.11035</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.00771</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.09546</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.12916</v>
       </c>
     </row>
   </sheetData>
